--- a/rawDataset_SAL.xlsx
+++ b/rawDataset_SAL.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,31 +492,83 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>45803.50533846065</v>
+        <v>45805.4808815162</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>923.02</v>
+      </c>
+      <c r="H2" t="n">
+        <v>553.8127329953206</v>
+      </c>
+      <c r="I2" t="n">
+        <v>49.28323032379151</v>
+      </c>
+      <c r="J2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="b">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>45805.48993398148</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>192.94</v>
+      </c>
+      <c r="H3" t="n">
+        <v>115.7657927190828</v>
+      </c>
+      <c r="I3" t="n">
+        <v>55.5261316</v>
+      </c>
+      <c r="J3" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>45805.49028493056</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Exceeded Max.</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>16233.08272033584</v>
-      </c>
-      <c r="I2" t="n">
-        <v>50.74465980529785</v>
-      </c>
-      <c r="J2" t="n">
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>192.94</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>115.7657927190828</v>
+      </c>
+      <c r="I4" t="n">
+        <v>55.5261316</v>
+      </c>
+      <c r="J4" t="n">
         <v>100</v>
       </c>
     </row>
@@ -531,7 +583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,15 +655,10 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>45803.50533846065</v>
+        <v>45805.4808815162</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -631,9 +678,80 @@
         <v>0.2</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>45805.48993398148</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>45805.49028493056</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -650,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -712,34 +830,92 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>45803.50533846066</v>
+        <v>45805.4808815162</v>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>49.18534473419189</v>
+      </c>
+      <c r="G2" t="n">
+        <v>49.11831077575684</v>
+      </c>
+      <c r="H2" t="n">
+        <v>49.29465633392334</v>
+      </c>
+      <c r="I2" t="n">
+        <v>49.38225852966308</v>
+      </c>
+      <c r="J2" t="n">
+        <v>35.62236560439308</v>
+      </c>
+      <c r="K2" t="n">
+        <v>49.14078224182129</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>45805.48993398148</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>51.83446896602783</v>
+      </c>
+      <c r="G3" t="n">
+        <v>56.45973579999998</v>
+      </c>
+      <c r="H3" t="n">
+        <v>57.74133099999999</v>
+      </c>
+      <c r="I3" t="n">
+        <v>57.03515119999998</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>45805.49028493495</v>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>49.92919914245606</v>
-      </c>
-      <c r="G2" t="n">
-        <v>49.75513774871826</v>
-      </c>
-      <c r="H2" t="n">
-        <v>49.84045448303223</v>
-      </c>
-      <c r="I2" t="n">
-        <v>50.44033779144287</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>51.83446896602783</v>
+      </c>
+      <c r="G4" t="n">
+        <v>56.45973579999998</v>
+      </c>
+      <c r="H4" t="n">
+        <v>57.74133099999999</v>
+      </c>
+      <c r="I4" t="n">
+        <v>57.03515119999998</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
